--- a/tables/datas/common/#MapConfig-地图配置表.xlsx
+++ b/tables/datas/common/#MapConfig-地图配置表.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -506,13 +506,6 @@
           <t>##group</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -580,6 +573,60 @@
         <v>25</v>
       </c>
       <c r="H5" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" t="n">
+        <v>2</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>senlin</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>迷雾森林</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>50</v>
+      </c>
+      <c r="F6" t="n">
+        <v>50</v>
+      </c>
+      <c r="G6" t="n">
+        <v>25</v>
+      </c>
+      <c r="H6" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" t="n">
+        <v>3</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>shanmai</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>断罪山脉</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>50</v>
+      </c>
+      <c r="F7" t="n">
+        <v>50</v>
+      </c>
+      <c r="G7" t="n">
+        <v>25</v>
+      </c>
+      <c r="H7" t="n">
         <v>25</v>
       </c>
     </row>

--- a/tables/datas/common/#MapConfig-地图配置表.xlsx
+++ b/tables/datas/common/#MapConfig-地图配置表.xlsx
@@ -555,7 +555,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>xinshoucun</t>
+          <t>新手村</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">

--- a/tables/datas/common/#MapConfig-地图配置表.xlsx
+++ b/tables/datas/common/#MapConfig-地图配置表.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -630,6 +630,33 @@
         <v>25</v>
       </c>
     </row>
+    <row r="8">
+      <c r="B8" t="n">
+        <v>4</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>落叶乡</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>落叶乡</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100</v>
+      </c>
+      <c r="F8" t="n">
+        <v>100</v>
+      </c>
+      <c r="G8" t="n">
+        <v>50</v>
+      </c>
+      <c r="H8" t="n">
+        <v>50</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/tables/datas/common/#MapConfig-地图配置表.xlsx
+++ b/tables/datas/common/#MapConfig-地图配置表.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -551,16 +551,16 @@
     </row>
     <row r="5">
       <c r="B5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>新手村</t>
+          <t>senlin</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>新手村</t>
+          <t>迷雾森林</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -578,16 +578,16 @@
     </row>
     <row r="6">
       <c r="B6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>senlin</t>
+          <t>shanmai</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>迷雾森林</t>
+          <t>断罪山脉</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -605,56 +605,56 @@
     </row>
     <row r="7">
       <c r="B7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>shanmai</t>
+          <t>落叶乡</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>断罪山脉</t>
+          <t>落叶乡</t>
         </is>
       </c>
       <c r="E7" t="n">
+        <v>100</v>
+      </c>
+      <c r="F7" t="n">
+        <v>100</v>
+      </c>
+      <c r="G7" t="n">
         <v>50</v>
       </c>
-      <c r="F7" t="n">
+      <c r="H7" t="n">
         <v>50</v>
-      </c>
-      <c r="G7" t="n">
-        <v>25</v>
-      </c>
-      <c r="H7" t="n">
-        <v>25</v>
       </c>
     </row>
     <row r="8">
       <c r="B8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>落叶乡</t>
+          <t>野狼谷</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>落叶乡</t>
+          <t>野狼谷</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="F8" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="G8" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="H8" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
     </row>
   </sheetData>
